--- a/source_data/Figure2/Figure2_SourceData.xlsx
+++ b/source_data/Figure2/Figure2_SourceData.xlsx
@@ -7,18 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig3A_arrays" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule2_selected" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule2_all_candidates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig3B_conditions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig3B_measurements" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure_sizes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5_structure_layout" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5_molecular_points" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5_reaction_layout" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retained_v3_numbers" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Printed_numbers" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Printed_numbers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig3A_arrays" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule2_selected" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rule2_all_candidates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig3B_conditions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig3B_measurements" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure_sizes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V6_summary_points" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,6 +436,3076 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G87"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="51" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>display</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>source_field</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>source_selection</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Buchwald-Hartwig|1: share</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>32.65108839071612</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>screen=Buchwald-Hartwig|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Buchwald-Hartwig|1: combination</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>66.02170660680888</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>screen=Buchwald-Hartwig|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Buchwald-Hartwig|1: noise</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.327205002475</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>screen=Buchwald-Hartwig|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Buchwald-Hartwig|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24.43729299104108</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>screen=Buchwald-Hartwig|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Buchwald-Hartwig|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>8.21379539967503</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>screen=Buchwald-Hartwig|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Buchwald-Hartwig|2: share</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>38.89741053407848</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>screen=Buchwald-Hartwig|2; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Buchwald-Hartwig|2: combination</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>59.59323746433078</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>screen=Buchwald-Hartwig|2; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Buchwald-Hartwig|2: noise</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1.50935200159074</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>screen=Buchwald-Hartwig|2; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Buchwald-Hartwig|2: owner_share</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>39.05135787038115</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>screen=Buchwald-Hartwig|2; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Buchwald-Hartwig|2: partner_share</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.15394733630266</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>screen=Buchwald-Hartwig|2; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C-O competitive reactions|1: share</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4.14178035812805</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>screen=C-O competitive reactions|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C-O competitive reactions|1: combination</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>92.93409259053372</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>screen=C-O competitive reactions|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>C-O competitive reactions|1: noise</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2.9241270513382</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>screen=C-O competitive reactions|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>C-O competitive reactions|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>9.93550174029577</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>screen=C-O competitive reactions|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C-O competitive reactions|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>-5.79372138216771</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>screen=C-O competitive reactions|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Heck|1: share</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>34.61906606519625</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>screen=Heck|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Heck|1: combination</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>63.50678482401185</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>screen=Heck|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Heck|1: noise</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1.87414911079191</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>screen=Heck|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Heck|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>27.85014545257872</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>screen=Heck|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Heck|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6.76892061261753</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>screen=Heck|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hiyama|1: share</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>31.93331436940704</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>screen=Hiyama|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Hiyama|1: combination</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>61.25541819136987</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>screen=Hiyama|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Hiyama|1: noise</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>6.81126743922308</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>screen=Hiyama|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Hiyama|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>20.02038970798244</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>screen=Hiyama|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Hiyama|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>11.91292466142459</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>screen=Hiyama|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kumada|1: share</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>42.19007464416531</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>screen=Kumada|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kumada|1: combination</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>55.32946474678738</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>screen=Kumada|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kumada|1: noise</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2.4804606090473</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>screen=Kumada|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kumada|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>33.88896308990812</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>screen=Kumada|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kumada|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>8.30111155425719</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>screen=Kumada|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SNAr|1: share</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>45.90857086572984</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>screen=SNAr|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SNAr|1: combination</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>51.62999704512481</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>screen=SNAr|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SNAr|1: noise</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2.46143208914535</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>screen=SNAr|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SNAr|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>45.56489916535027</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>screen=SNAr|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SNAr|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.34367170037956</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>screen=SNAr|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sonogashira|1: share</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>35.15508818276449</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>screen=Sonogashira|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sonogashira|1: combination</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>62.63518659810286</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>screen=Sonogashira|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sonogashira|1: noise</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2.20972521913266</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>screen=Sonogashira|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sonogashira|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>24.20444863819758</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>screen=Sonogashira|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sonogashira|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>10.9506395445669</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>screen=Sonogashira|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Suzuki|1: share</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>30.85780770328467</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>screen=Suzuki|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Suzuki|1: combination</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>66.86996304257498</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>screen=Suzuki|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Suzuki|1: noise</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2.27222925414035</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>screen=Suzuki|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Suzuki|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>24.8142172627361</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>screen=Suzuki|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Suzuki|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>6.04359044054856</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>screen=Suzuki|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ullmann|1: share</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>25.15174414836362</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>screen=Ullmann|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ullmann|1: combination</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>72.84728853045051</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>screen=Ullmann|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ullmann|1: noise</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2.00096732118585</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>screen=Ullmann|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ullmann|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>29.88171749240014</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>screen=Ullmann|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ullmann|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-4.729973344036519</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>screen=Ullmann|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Acylation|1: share</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>42.81144462883166</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>screen=Acylation|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Acylation|1: combination</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>54.17632052824113</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>screen=Acylation|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Acylation|1: noise</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>3.0122348429272</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>screen=Acylation|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Acylation|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>29.98313019179326</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>screen=Acylation|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Acylation|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>12.8283144370384</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>screen=Acylation|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chan-Lam|1: share</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>28.96392438234972</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>screen=Chan-Lam|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Chan-Lam|1: combination</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>67.97080460494026</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>screen=Chan-Lam|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Chan-Lam|1: noise</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3.06527101271001</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>screen=Chan-Lam|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Chan-Lam|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>15.90390467316881</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>screen=Chan-Lam|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Chan-Lam|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>13.06001970918091</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>screen=Chan-Lam|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Esterification|1: share</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>39.03384876664993</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>screen=Esterification|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Esterification|1: combination</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>59.2771098329551</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>screen=Esterification|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Esterification|1: noise</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1.68904140039497</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>screen=Esterification|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Esterification|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>38.91622507131059</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>screen=Esterification|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Esterification|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.11762369533934</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>screen=Esterification|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Grignard|1: share</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6.88239547619672</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>screen=Grignard|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Grignard|1: combination</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>87.36733588731188</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>screen=Grignard|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Grignard|1: noise</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>5.75026863649138</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>screen=Grignard|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Grignard|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>5.53833541950736</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>screen=Grignard|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Grignard|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1.34406005668936</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>screen=Grignard|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Reductive-amination|1: share</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>29.61504560578293</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>screen=Reductive-amination|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Reductive-amination|1: combination</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>66.8706291454648</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>combination</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>screen=Reductive-amination|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Reductive-amination|1: noise</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>3.51432524875226</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>screen=Reductive-amination|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Reductive-amination|1: owner_share</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>16.9485181286621</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>screen=Reductive-amination|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Reductive-amination|1: partner_share</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>12.66652747712082</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>bar length</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>screen=Reductive-amination|1; 100 * frozen fraction; signed values retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>halide arrays with halide owner</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>10</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>electrophile_role,owner_role</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>electrophile_role is finite; existing frozen owner role is electrophile</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>median molecular share</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>32.65108839071612</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>median across all 15 arrays; nearest percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>median owner fraction</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>80.41471222239403</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>median across all 15 arrays; nearest percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SNAr owner_share</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>45.56489916535027</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>45.6%</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>owner_share</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>screen=SNAr|1; one decimal percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SNAr partner_share</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0.34367170037956</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>partner_share</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>screen=SNAr|1; one decimal percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>measured combinations</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>47</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>10_PUBLIC_RELEASE_CANDIDATE/data/conditions.csv</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>condition_id</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>rxn_class=SNAr; unique measured additive-solvent cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>composition axis tick</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>06_CODE/Figures/figure3.py</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>percentage coordinate scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>composition axis tick</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>100</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>06_CODE/Figures/figure3.py</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>percentage coordinate scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>role share axis tick</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>06_CODE/Figures/figure3.py</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>percentage coordinate scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>role share axis tick</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>20</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>06_CODE/Figures/figure3.py</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>percentage coordinate scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>role share axis tick</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>40</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>06_CODE/Figures/figure3.py</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>percentage coordinate scale</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AR16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2995,3725 +6062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>x_mm</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>y_mm</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>width_mm</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>height_mm</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>atom_font_pt</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>native_subscript_font_pt</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>common_bond_mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>halide</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/Fig2_B_halide.svg</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>139.7525058737471</v>
-      </c>
-      <c r="D2" t="n">
-        <v>54.96750301624849</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23.49498825250587</v>
-      </c>
-      <c r="F2" t="n">
-        <v>12.06499396750301</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4.064</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>nucleophile</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/Fig2_B_nucleophile.svg</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>142.7158377254145</v>
-      </c>
-      <c r="D3" t="n">
-        <v>78.17916957708188</v>
-      </c>
-      <c r="E3" t="n">
-        <v>17.56832454917106</v>
-      </c>
-      <c r="F3" t="n">
-        <v>11.64166084583624</v>
-      </c>
-      <c r="G3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.064</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/Fig2_B_product.svg</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>135.307508096246</v>
-      </c>
-      <c r="D4" t="n">
-        <v>102.7925046037477</v>
-      </c>
-      <c r="E4" t="n">
-        <v>32.38498380750809</v>
-      </c>
-      <c r="F4" t="n">
-        <v>18.4149907925046</v>
-      </c>
-      <c r="G4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4.064</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G87"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="51" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>panel</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>display</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>source_file</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>source_field</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>source_selection</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Buchwald-Hartwig|1: share</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>32.65108839071612</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>screen=Buchwald-Hartwig|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Buchwald-Hartwig|1: combination</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>66.02170660680888</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>screen=Buchwald-Hartwig|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Buchwald-Hartwig|1: noise</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1.327205002475</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>screen=Buchwald-Hartwig|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Buchwald-Hartwig|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>24.43729299104108</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>screen=Buchwald-Hartwig|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Buchwald-Hartwig|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>8.21379539967503</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>screen=Buchwald-Hartwig|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Buchwald-Hartwig|2: share</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>38.89741053407848</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>screen=Buchwald-Hartwig|2; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Buchwald-Hartwig|2: combination</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>59.59323746433078</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>screen=Buchwald-Hartwig|2; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Buchwald-Hartwig|2: noise</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1.50935200159074</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>screen=Buchwald-Hartwig|2; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Buchwald-Hartwig|2: owner_share</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>39.05135787038115</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>screen=Buchwald-Hartwig|2; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Buchwald-Hartwig|2: partner_share</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.15394733630266</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>screen=Buchwald-Hartwig|2; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>C-O competitive reactions|1: share</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>4.14178035812805</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>screen=C-O competitive reactions|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>C-O competitive reactions|1: combination</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>92.93409259053372</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>screen=C-O competitive reactions|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>C-O competitive reactions|1: noise</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2.9241270513382</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>screen=C-O competitive reactions|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>C-O competitive reactions|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>9.93550174029577</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>screen=C-O competitive reactions|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>C-O competitive reactions|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>-5.79372138216771</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>screen=C-O competitive reactions|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Heck|1: share</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>34.61906606519625</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>screen=Heck|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Heck|1: combination</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>63.50678482401185</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>screen=Heck|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Heck|1: noise</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1.87414911079191</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>screen=Heck|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Heck|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>27.85014545257872</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>screen=Heck|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Heck|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>6.76892061261753</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>screen=Heck|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Hiyama|1: share</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>31.93331436940704</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>screen=Hiyama|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Hiyama|1: combination</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>61.25541819136987</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>screen=Hiyama|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Hiyama|1: noise</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>6.81126743922308</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>screen=Hiyama|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Hiyama|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>20.02038970798244</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>screen=Hiyama|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Hiyama|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>11.91292466142459</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>screen=Hiyama|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Kumada|1: share</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>42.19007464416531</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>screen=Kumada|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Kumada|1: combination</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>55.32946474678738</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>screen=Kumada|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Kumada|1: noise</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>2.4804606090473</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>screen=Kumada|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Kumada|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>33.88896308990812</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>screen=Kumada|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Kumada|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>8.30111155425719</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>screen=Kumada|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>SNAr|1: share</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>45.90857086572984</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>screen=SNAr|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>SNAr|1: combination</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>51.62999704512481</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>screen=SNAr|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>SNAr|1: noise</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>2.46143208914535</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>screen=SNAr|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>SNAr|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>45.56489916535027</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>screen=SNAr|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>SNAr|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0.34367170037956</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>screen=SNAr|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Sonogashira|1: share</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>35.15508818276449</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>screen=Sonogashira|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Sonogashira|1: combination</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>62.63518659810286</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>screen=Sonogashira|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Sonogashira|1: noise</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2.20972521913266</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>screen=Sonogashira|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Sonogashira|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>24.20444863819758</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>screen=Sonogashira|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Sonogashira|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>10.9506395445669</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>screen=Sonogashira|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Suzuki|1: share</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>30.85780770328467</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>screen=Suzuki|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Suzuki|1: combination</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>66.86996304257498</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>screen=Suzuki|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Suzuki|1: noise</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>2.27222925414035</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>screen=Suzuki|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Suzuki|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>24.8142172627361</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>screen=Suzuki|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Suzuki|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>6.04359044054856</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>screen=Suzuki|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Ullmann|1: share</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>25.15174414836362</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>screen=Ullmann|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Ullmann|1: combination</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>72.84728853045051</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>screen=Ullmann|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Ullmann|1: noise</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>2.00096732118585</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>screen=Ullmann|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Ullmann|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>29.88171749240014</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>screen=Ullmann|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Ullmann|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>-4.729973344036519</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>screen=Ullmann|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Acylation|1: share</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>42.81144462883166</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>screen=Acylation|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Acylation|1: combination</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>54.17632052824113</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>screen=Acylation|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Acylation|1: noise</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>3.0122348429272</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>screen=Acylation|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Acylation|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>29.98313019179326</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>screen=Acylation|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Acylation|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>12.8283144370384</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>screen=Acylation|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Chan-Lam|1: share</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>28.96392438234972</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>screen=Chan-Lam|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Chan-Lam|1: combination</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>67.97080460494026</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>screen=Chan-Lam|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Chan-Lam|1: noise</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>3.06527101271001</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>screen=Chan-Lam|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Chan-Lam|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>15.90390467316881</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>screen=Chan-Lam|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Chan-Lam|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>13.06001970918091</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>screen=Chan-Lam|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Esterification|1: share</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>39.03384876664993</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>screen=Esterification|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Esterification|1: combination</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>59.2771098329551</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>screen=Esterification|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Esterification|1: noise</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>1.68904140039497</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>screen=Esterification|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Esterification|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>38.91622507131059</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>screen=Esterification|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Esterification|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>0.11762369533934</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>screen=Esterification|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Grignard|1: share</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>6.88239547619672</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>screen=Grignard|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Grignard|1: combination</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>87.36733588731188</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>screen=Grignard|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Grignard|1: noise</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>5.75026863649138</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>screen=Grignard|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Grignard|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>5.53833541950736</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>screen=Grignard|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Grignard|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>1.34406005668936</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>screen=Grignard|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Reductive-amination|1: share</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>29.61504560578293</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>screen=Reductive-amination|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Reductive-amination|1: combination</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>66.8706291454648</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>combination</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>screen=Reductive-amination|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Reductive-amination|1: noise</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>3.51432524875226</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>noise</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>screen=Reductive-amination|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Reductive-amination|1: owner_share</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>16.9485181286621</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>screen=Reductive-amination|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Reductive-amination|1: partner_share</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>12.66652747712082</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>bar length</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>screen=Reductive-amination|1; 100 * frozen fraction; signed values retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>halide arrays with halide owner</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>10</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>electrophile_role,owner_role</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>electrophile_role is finite; existing frozen owner role is electrophile</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>median molecular share</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>32.65108839071612</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>median across all 15 arrays; nearest percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>median owner fraction</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>80.41471222239403</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>owner_fraction</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>median across all 15 arrays; nearest percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>SNAr owner_share</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>45.56489916535027</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>45.6%</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>owner_share</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>screen=SNAr|1; one decimal percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>SNAr partner_share</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>0.34367170037956</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>05_DATA/Results/display_inputs/Anatomy_arrays.csv</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>partner_share</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>screen=SNAr|1; one decimal percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>measured combinations</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>47</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>10_PUBLIC_RELEASE_CANDIDATE/data/conditions.csv</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>condition_id</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>rxn_class=SNAr; unique measured additive-solvent cells</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>composition axis tick</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>06_CODE/Figures/figure3.py</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>percentage coordinate scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>composition axis tick</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>100</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>06_CODE/Figures/figure3.py</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>percentage coordinate scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>role share axis tick</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>06_CODE/Figures/figure3.py</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>percentage coordinate scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>role share axis tick</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>20</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>06_CODE/Figures/figure3.py</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>percentage coordinate scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>role share axis tick</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>40</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>06_CODE/Figures/figure3.py</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>percentage coordinate scale</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>panel</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>display</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>source_file</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>source_field</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>source_selection</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>display_transform</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SNAr owner share</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.4556489916535027</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>45.6%</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>05_DATA/Analysis/figure_display/v5_reference_tables/screen_shares.xlsx</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Fig3A_arrays:owner_share</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>screen=SNAr|1; source fraction; display percent</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>fraction</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100 * value</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SNAr partner share</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.0034367170037956</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>05_DATA/Analysis/figure_display/v5_reference_tables/screen_shares.xlsx</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Fig3A_arrays:partner_share</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>screen=SNAr|1; source fraction; display percent</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>fraction</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100 * value</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>median molecular share</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.3265108839071612</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>05_DATA/Analysis/figure_display/v5_reference_tables/screen_shares.xlsx</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Fig3A_arrays:share</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>median of 15 source fractions; display percent</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>fraction</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100 * value</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>axis tick</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>05_DATA/Analysis/figure_display/v5_reference_tables/screen_shares.xlsx</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>display coordinate</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>percentage coordinate scale</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>percent coordinate</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>axis tick</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>05_DATA/Analysis/figure_display/v5_reference_tables/screen_shares.xlsx</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>display coordinate</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>percentage coordinate scale</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>percent coordinate</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>axis tick</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>40</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>05_DATA/Analysis/figure_display/v5_reference_tables/screen_shares.xlsx</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>display coordinate</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>percentage coordinate scale</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>percent coordinate</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>axis tick</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>05_DATA/Analysis/figure_display/v5_reference_tables/screen_shares.xlsx</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>display coordinate</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>percentage coordinate scale</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>percent coordinate</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>axis tick</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>25</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>05_DATA/Analysis/figure_display/v5_reference_tables/screen_shares.xlsx</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>display coordinate</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>percentage coordinate scale</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>percent coordinate</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>axis tick</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>05_DATA/Analysis/figure_display/v5_reference_tables/screen_shares.xlsx</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>display coordinate</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>percentage coordinate scale</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>percent coordinate</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7655,7 +7004,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -46881,7 +46230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -51482,7 +50831,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -52946,7 +52295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -53717,7 +53066,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -53843,1045 +53192,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>screen</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>center_y_mm</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>structure_x_mm</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>structure_y_mm</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>structure_width_mm</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>structure_height_mm</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>row_top_mm</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>row_bottom_mm</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>atom_font_pt</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>native_subscript_font_pt</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>common_bond_mm</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>owner_share_pct</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>partner_share_pct</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>visible_left_mm</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>visible_top_mm</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>visible_right_mm</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>visible_bottom_mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Buchwald-Hartwig|1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner01.svg</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>9.575015022792483</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.69787685633501</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2.804487613356186</v>
-      </c>
-      <c r="F2" t="n">
-        <v>21.58998920500539</v>
-      </c>
-      <c r="G2" t="n">
-        <v>12.69999365000317</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>15.95003004558497</v>
-      </c>
-      <c r="J2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L2" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M2" t="n">
-        <v>24.43729299104108</v>
-      </c>
-      <c r="N2" t="n">
-        <v>8.21379539967503</v>
-      </c>
-      <c r="O2" t="n">
-        <v>43.36085885817734</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.575000000000016</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>63.63914114182266</v>
-      </c>
-      <c r="R2" t="n">
-        <v>15.57503004558495</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Buchwald-Hartwig|2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner02.svg</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>23.34069909567961</v>
-      </c>
-      <c r="D3" t="n">
-        <v>42.28163534001567</v>
-      </c>
-      <c r="E3" t="n">
-        <v>15.73725697116318</v>
-      </c>
-      <c r="F3" t="n">
-        <v>22.43665544833894</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14.60499269750365</v>
-      </c>
-      <c r="H3" t="n">
-        <v>15.95003004558497</v>
-      </c>
-      <c r="I3" t="n">
-        <v>30.73136814577425</v>
-      </c>
-      <c r="J3" t="n">
-        <v>8</v>
-      </c>
-      <c r="K3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M3" t="n">
-        <v>39.05135787038115</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-0.15394733630266</v>
-      </c>
-      <c r="O3" t="n">
-        <v>42.85175555555556</v>
-      </c>
-      <c r="P3" t="n">
-        <v>16.32503004558495</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>64.14824444444444</v>
-      </c>
-      <c r="R3" t="n">
-        <v>30.35636814577427</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C-O competitive reactions|1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner03.svg</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>36.09038342256663</v>
-      </c>
-      <c r="D4" t="n">
-        <v>44.60892099848534</v>
-      </c>
-      <c r="E4" t="n">
-        <v>30.37818856329737</v>
-      </c>
-      <c r="F4" t="n">
-        <v>17.77999111000444</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10.7949946025027</v>
-      </c>
-      <c r="H4" t="n">
-        <v>30.73136814577425</v>
-      </c>
-      <c r="I4" t="n">
-        <v>41.44939869935901</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M4" t="n">
-        <v>9.93550174029577</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-5.79372138216771</v>
-      </c>
-      <c r="O4" t="n">
-        <v>45.26227428847537</v>
-      </c>
-      <c r="P4" t="n">
-        <v>31.10636814577424</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>61.73772571152465</v>
-      </c>
-      <c r="R4" t="n">
-        <v>41.07439869935899</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Heck|1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner04.svg</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>46.92909836138417</v>
-      </c>
-      <c r="D5" t="n">
-        <v>43.12563265047368</v>
-      </c>
-      <c r="E5" t="n">
-        <v>40.93681842106579</v>
-      </c>
-      <c r="F5" t="n">
-        <v>20.74332296167185</v>
-      </c>
-      <c r="G5" t="n">
-        <v>11.21832772416947</v>
-      </c>
-      <c r="H5" t="n">
-        <v>41.44939869935902</v>
-      </c>
-      <c r="I5" t="n">
-        <v>52.40879802340933</v>
-      </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M5" t="n">
-        <v>27.85014545257872</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6.76892061261753</v>
-      </c>
-      <c r="O5" t="n">
-        <v>43.86082893287555</v>
-      </c>
-      <c r="P5" t="n">
-        <v>41.82439869935899</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>63.13917106712447</v>
-      </c>
-      <c r="R5" t="n">
-        <v>52.0337980234093</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Hiyama|1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner05.svg</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>58.97572763711119</v>
-      </c>
-      <c r="D6" t="n">
-        <v>45.66858253557207</v>
-      </c>
-      <c r="E6" t="n">
-        <v>52.20519674787664</v>
-      </c>
-      <c r="F6" t="n">
-        <v>15.66332550167058</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12.91166021083656</v>
-      </c>
-      <c r="H6" t="n">
-        <v>52.40879802340933</v>
-      </c>
-      <c r="I6" t="n">
-        <v>65.54265725081305</v>
-      </c>
-      <c r="J6" t="n">
-        <v>8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20.02038970798244</v>
-      </c>
-      <c r="N6" t="n">
-        <v>11.91292466142459</v>
-      </c>
-      <c r="O6" t="n">
-        <v>46.29726555555555</v>
-      </c>
-      <c r="P6" t="n">
-        <v>52.78379802340933</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>60.70273444444445</v>
-      </c>
-      <c r="R6" t="n">
-        <v>65.16765725081308</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Kumada|1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner06.svg</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>70.90132680890743</v>
-      </c>
-      <c r="D7" t="n">
-        <v>43.12284139325691</v>
-      </c>
-      <c r="E7" t="n">
-        <v>65.2028832238917</v>
-      </c>
-      <c r="F7" t="n">
-        <v>20.74332296167185</v>
-      </c>
-      <c r="G7" t="n">
-        <v>10.7949946025027</v>
-      </c>
-      <c r="H7" t="n">
-        <v>65.54265725081304</v>
-      </c>
-      <c r="I7" t="n">
-        <v>76.25999636700182</v>
-      </c>
-      <c r="J7" t="n">
-        <v>8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>6</v>
-      </c>
-      <c r="L7" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M7" t="n">
-        <v>33.88896308990812</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8.30111155425719</v>
-      </c>
-      <c r="O7" t="n">
-        <v>43.8474786987966</v>
-      </c>
-      <c r="P7" t="n">
-        <v>65.91765725081302</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>63.15252130120341</v>
-      </c>
-      <c r="R7" t="n">
-        <v>75.8849963670018</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SNAr|1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner07.svg</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>83.49616845235329</v>
-      </c>
-      <c r="D8" t="n">
-        <v>44.82834128002572</v>
-      </c>
-      <c r="E8" t="n">
-        <v>76.15874731950134</v>
-      </c>
-      <c r="F8" t="n">
-        <v>17.35665798833767</v>
-      </c>
-      <c r="G8" t="n">
-        <v>14.18165957583688</v>
-      </c>
-      <c r="H8" t="n">
-        <v>76.25999636700183</v>
-      </c>
-      <c r="I8" t="n">
-        <v>90.73234053770474</v>
-      </c>
-      <c r="J8" t="n">
-        <v>8</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M8" t="n">
-        <v>45.56489916535027</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.34367170037956</v>
-      </c>
-      <c r="O8" t="n">
-        <v>45.44150165445387</v>
-      </c>
-      <c r="P8" t="n">
-        <v>76.63499636700183</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>61.55849834554615</v>
-      </c>
-      <c r="R8" t="n">
-        <v>90.35734053770474</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sonogashira|1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner08.svg</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>96.88005383904392</v>
-      </c>
-      <c r="D9" t="n">
-        <v>42.70128484671434</v>
-      </c>
-      <c r="E9" t="n">
-        <v>90.53085571717216</v>
-      </c>
-      <c r="F9" t="n">
-        <v>21.58998920500539</v>
-      </c>
-      <c r="G9" t="n">
-        <v>12.06499396750301</v>
-      </c>
-      <c r="H9" t="n">
-        <v>90.73234053770474</v>
-      </c>
-      <c r="I9" t="n">
-        <v>103.0277671403831</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M9" t="n">
-        <v>24.20444863819758</v>
-      </c>
-      <c r="N9" t="n">
-        <v>10.9506395445669</v>
-      </c>
-      <c r="O9" t="n">
-        <v>43.40543599463878</v>
-      </c>
-      <c r="P9" t="n">
-        <v>91.10734053770473</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>63.59456400536122</v>
-      </c>
-      <c r="R9" t="n">
-        <v>102.6527671403831</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Suzuki|1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner09.svg</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>110.5220328829502</v>
-      </c>
-      <c r="D10" t="n">
-        <v>45.24222718255224</v>
-      </c>
-      <c r="E10" t="n">
-        <v>102.6915219495724</v>
-      </c>
-      <c r="F10" t="n">
-        <v>16.50999174500413</v>
-      </c>
-      <c r="G10" t="n">
-        <v>15.02832581917042</v>
-      </c>
-      <c r="H10" t="n">
-        <v>103.0277671403831</v>
-      </c>
-      <c r="I10" t="n">
-        <v>118.0162986255174</v>
-      </c>
-      <c r="J10" t="n">
-        <v>8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M10" t="n">
-        <v>24.8142172627361</v>
-      </c>
-      <c r="N10" t="n">
-        <v>6.04359044054856</v>
-      </c>
-      <c r="O10" t="n">
-        <v>46.01129223135306</v>
-      </c>
-      <c r="P10" t="n">
-        <v>103.4027671403831</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>60.98870776864695</v>
-      </c>
-      <c r="R10" t="n">
-        <v>117.6412986255174</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Ullmann|1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner10.svg</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>123.3753139023098</v>
-      </c>
-      <c r="D11" t="n">
-        <v>44.60892099848534</v>
-      </c>
-      <c r="E11" t="n">
-        <v>117.6631190430405</v>
-      </c>
-      <c r="F11" t="n">
-        <v>17.77999111000444</v>
-      </c>
-      <c r="G11" t="n">
-        <v>10.7949946025027</v>
-      </c>
-      <c r="H11" t="n">
-        <v>118.0162986255174</v>
-      </c>
-      <c r="I11" t="n">
-        <v>128.7343291791021</v>
-      </c>
-      <c r="J11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M11" t="n">
-        <v>29.88171749240014</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-4.729973344036519</v>
-      </c>
-      <c r="O11" t="n">
-        <v>45.26227428847537</v>
-      </c>
-      <c r="P11" t="n">
-        <v>118.3912986255174</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>61.73772571152465</v>
-      </c>
-      <c r="R11" t="n">
-        <v>128.3593291791021</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Acylation|1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner11.svg</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>135.0171019376291</v>
-      </c>
-      <c r="D12" t="n">
-        <v>47.36078613335027</v>
-      </c>
-      <c r="E12" t="n">
-        <v>129.551564002568</v>
-      </c>
-      <c r="F12" t="n">
-        <v>12.2766605283364</v>
-      </c>
-      <c r="G12" t="n">
-        <v>10.7949946025027</v>
-      </c>
-      <c r="H12" t="n">
-        <v>129.9343291791021</v>
-      </c>
-      <c r="I12" t="n">
-        <v>140.099874696156</v>
-      </c>
-      <c r="J12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L12" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M12" t="n">
-        <v>29.98313019179326</v>
-      </c>
-      <c r="N12" t="n">
-        <v>12.8283144370384</v>
-      </c>
-      <c r="O12" t="n">
-        <v>47.99229222222223</v>
-      </c>
-      <c r="P12" t="n">
-        <v>130.3093291791021</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>59.00770777777779</v>
-      </c>
-      <c r="R12" t="n">
-        <v>139.724874696156</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Chan-Lam|1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner12.svg</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>147.9996216481575</v>
-      </c>
-      <c r="D13" t="n">
-        <v>40.60319641080388</v>
-      </c>
-      <c r="E13" t="n">
-        <v>139.6775913727143</v>
-      </c>
-      <c r="F13" t="n">
-        <v>25.82332042167312</v>
-      </c>
-      <c r="G13" t="n">
-        <v>15.87499206250397</v>
-      </c>
-      <c r="H13" t="n">
-        <v>140.099874696156</v>
-      </c>
-      <c r="I13" t="n">
-        <v>155.8993686001591</v>
-      </c>
-      <c r="J13" t="n">
-        <v>8</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M13" t="n">
-        <v>15.90390467316881</v>
-      </c>
-      <c r="N13" t="n">
-        <v>13.06001970918091</v>
-      </c>
-      <c r="O13" t="n">
-        <v>41.36452133523309</v>
-      </c>
-      <c r="P13" t="n">
-        <v>140.474874696156</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>65.63547866476692</v>
-      </c>
-      <c r="R13" t="n">
-        <v>155.5243686001591</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Esterification|1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner13.svg</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>165.6579238882606</v>
-      </c>
-      <c r="D14" t="n">
-        <v>41.00866629655352</v>
-      </c>
-      <c r="E14" t="n">
-        <v>155.5194185888841</v>
-      </c>
-      <c r="F14" t="n">
-        <v>24.97665417833958</v>
-      </c>
-      <c r="G14" t="n">
-        <v>20.10832327917169</v>
-      </c>
-      <c r="H14" t="n">
-        <v>155.8993686001591</v>
-      </c>
-      <c r="I14" t="n">
-        <v>175.4164791763621</v>
-      </c>
-      <c r="J14" t="n">
-        <v>8</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M14" t="n">
-        <v>38.91622507131059</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.11762369533934</v>
-      </c>
-      <c r="O14" t="n">
-        <v>41.73373856735073</v>
-      </c>
-      <c r="P14" t="n">
-        <v>156.2743686001591</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>65.26626143264929</v>
-      </c>
-      <c r="R14" t="n">
-        <v>175.0414791763621</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Grignard|1</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner14.svg</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>184.167411452771</v>
-      </c>
-      <c r="D15" t="n">
-        <v>45.66794753557208</v>
-      </c>
-      <c r="E15" t="n">
-        <v>174.9834855249423</v>
-      </c>
-      <c r="F15" t="n">
-        <v>15.66332550167058</v>
-      </c>
-      <c r="G15" t="n">
-        <v>17.56832454917106</v>
-      </c>
-      <c r="H15" t="n">
-        <v>175.4164791763621</v>
-      </c>
-      <c r="I15" t="n">
-        <v>192.9183437291799</v>
-      </c>
-      <c r="J15" t="n">
-        <v>8</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.53833541950736</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.34406005668936</v>
-      </c>
-      <c r="O15" t="n">
-        <v>46.28393055555556</v>
-      </c>
-      <c r="P15" t="n">
-        <v>175.7914791763621</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>60.71606944444444</v>
-      </c>
-      <c r="R15" t="n">
-        <v>192.5433437291798</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Reductive-amination|1</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>02_FIGURES/ChemDraw/v3/f3/Fig3_A_owner15.svg</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>200.8166725152238</v>
-      </c>
-      <c r="D16" t="n">
-        <v>34.87884053681775</v>
-      </c>
-      <c r="E16" t="n">
-        <v>192.5101785653458</v>
-      </c>
-      <c r="F16" t="n">
-        <v>37.25331470667597</v>
-      </c>
-      <c r="G16" t="n">
-        <v>15.87499206250397</v>
-      </c>
-      <c r="H16" t="n">
-        <v>192.9183437291799</v>
-      </c>
-      <c r="I16" t="n">
-        <v>208.7150013012678</v>
-      </c>
-      <c r="J16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>6</v>
-      </c>
-      <c r="L16" t="n">
-        <v>4.064</v>
-      </c>
-      <c r="M16" t="n">
-        <v>16.9485181286621</v>
-      </c>
-      <c r="N16" t="n">
-        <v>12.66652747712082</v>
-      </c>
-      <c r="O16" t="n">
-        <v>35.50257927041505</v>
-      </c>
-      <c r="P16" t="n">
-        <v>193.2933437291798</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>71.49742072958495</v>
-      </c>
-      <c r="R16" t="n">
-        <v>208.3400013012678</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -54892,17 +53220,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>molecular_share</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>plotted_share_pct</t>
+          <t>denominator</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>presentation_vertical_offset_mm</t>
+          <t>value_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>display_value_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>display_x_offset</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>overflow</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>display_marker</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>displayed_annotation</t>
         </is>
       </c>
     </row>
@@ -54912,15 +53265,34 @@
           <t>Buchwald-Hartwig|1</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.3265108839071612</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>32.65108839071612</v>
       </c>
-      <c r="D2" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="E2" t="n">
+        <v>32.65108839071612</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.1581395348837209</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -54928,15 +53300,34 @@
           <t>Buchwald-Hartwig|2</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0.3889741053407848</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>38.89741053407848</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="n">
+        <v>38.89741053407848</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -54944,15 +53335,34 @@
           <t>C-O competitive reactions|1</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0.0414178035812805</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>4.14178035812805</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="n">
+        <v>4.14178035812805</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -54960,15 +53370,34 @@
           <t>Heck|1</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.3461906606519625</v>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>34.61906606519625</v>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="n">
+        <v>34.61906606519625</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -54976,15 +53405,34 @@
           <t>Hiyama|1</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.3193331436940704</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>31.93331436940704</v>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="n">
+        <v>31.93331436940704</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1581395348837209</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -54992,15 +53440,34 @@
           <t>Kumada|1</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0.4219007464416531</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>42.19007464416531</v>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="n">
+        <v>42.19007464416531</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.07906976744186046</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -55008,15 +53475,34 @@
           <t>SNAr|1</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.4590857086572984</v>
-      </c>
-      <c r="C8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>45.90857086572984</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="n">
+        <v>45.90857086572984</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07906976744186046</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -55024,15 +53510,34 @@
           <t>Sonogashira|1</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.3515508818276449</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>35.15508818276449</v>
       </c>
-      <c r="D9" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="E9" t="n">
+        <v>35.15508818276449</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.07906976744186046</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -55040,15 +53545,34 @@
           <t>Suzuki|1</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0.3085780770328467</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>30.85780770328467</v>
       </c>
-      <c r="D10" t="n">
-        <v>-1.8</v>
-      </c>
+      <c r="E10" t="n">
+        <v>30.85780770328467</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.07906976744186046</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -55056,15 +53580,34 @@
           <t>Ullmann|1</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0.2515174414836362</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>25.15174414836362</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="n">
+        <v>25.15174414836362</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -55072,15 +53615,34 @@
           <t>Acylation|1</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0.4281144462883166</v>
-      </c>
-      <c r="C12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>42.81144462883166</v>
       </c>
-      <c r="D12" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="E12" t="n">
+        <v>42.81144462883166</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -55088,15 +53650,34 @@
           <t>Chan-Lam|1</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0.2896392438234972</v>
-      </c>
-      <c r="C13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>28.96392438234972</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="n">
+        <v>28.96392438234972</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.07906976744186046</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -55104,15 +53685,34 @@
           <t>Esterification|1</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>0.3903384876664993</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>39.03384876664993</v>
       </c>
-      <c r="D14" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="E14" t="n">
+        <v>39.03384876664993</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.07906976744186046</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -55120,15 +53720,34 @@
           <t>Grignard|1</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0.0688239547619672</v>
-      </c>
-      <c r="C15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>6.88239547619672</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="n">
+        <v>6.88239547619672</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.07906976744186046</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -55136,15 +53755,563 @@
           <t>Reductive-amination|1</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>0.2961504560578293</v>
-      </c>
-      <c r="C16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>total preference</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>29.61504560578293</v>
       </c>
-      <c r="D16" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="E16" t="n">
+        <v>29.61504560578293</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Buchwald-Hartwig|1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>74.8437316962135</v>
+      </c>
+      <c r="E17" t="n">
+        <v>74.8437316962135</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Buchwald-Hartwig|2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>100.395777853047</v>
+      </c>
+      <c r="E18" t="n">
+        <v>100.395777853047</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.07906976744186046</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C-O competitive reactions|1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>239.8848051128014</v>
+      </c>
+      <c r="E19" t="n">
+        <v>150</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>triangle</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>239.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Heck|1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>80.44741992788025</v>
+      </c>
+      <c r="E20" t="n">
+        <v>80.44741992788025</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.07906976744186046</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Hiyama|1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>62.69436825875646</v>
+      </c>
+      <c r="E21" t="n">
+        <v>62.69436825875646</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kumada|1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>80.32449189941124</v>
+      </c>
+      <c r="E22" t="n">
+        <v>80.32449189941124</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SNAr|1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>99.25139969748848</v>
+      </c>
+      <c r="E23" t="n">
+        <v>99.25139969748848</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sonogashira|1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>68.85048477865664</v>
+      </c>
+      <c r="E24" t="n">
+        <v>68.85048477865664</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Suzuki|1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>80.41471222239403</v>
+      </c>
+      <c r="E25" t="n">
+        <v>80.41471222239403</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.07906976744186046</v>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ullmann|1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>118.8057468942736</v>
+      </c>
+      <c r="E26" t="n">
+        <v>118.8057468942736</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Acylation|1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>70.035315210085</v>
+      </c>
+      <c r="E27" t="n">
+        <v>70.035315210085</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.07906976744186046</v>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chan-Lam|1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>54.90935711343201</v>
+      </c>
+      <c r="E28" t="n">
+        <v>54.90935711343201</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Esterification|1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>99.69866231730691</v>
+      </c>
+      <c r="E29" t="n">
+        <v>99.69866231730691</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.07906976744186046</v>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Grignard|1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>80.47104294808555</v>
+      </c>
+      <c r="E30" t="n">
+        <v>80.47104294808555</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.1581395348837209</v>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Reductive-amination|1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>owner_fraction</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>molecular share</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>57.22941762194203</v>
+      </c>
+      <c r="E31" t="n">
+        <v>57.22941762194203</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.07906976744186046</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
